--- a/CAPACITORGOODpuget/project/Address.xlsx
+++ b/CAPACITORGOODpuget/project/Address.xlsx
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="400">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -110,49 +110,49 @@
     <t>(!!! MUST FIX !!! - not allowed)</t>
   </si>
   <si>
+    <t>Floating pin V_GNDx.MINUS(0)</t>
+  </si>
+  <si>
+    <t>Floating pin VI__CAPGD.PLUS(59)</t>
+  </si>
+  <si>
+    <t>Xsim_CAPACITORGOODpuget_ROW8</t>
+  </si>
+  <si>
+    <t>Floating pin XCAPACITORGOODpuget1.ok_capacitorgood(ok_capacitorgood)</t>
+  </si>
+  <si>
+    <t>Floating pin XCAPACITORGOODpuget1.status_chrg_status_xdatamap1_6aa5ac6c(status_chrg_status_xdatamap1_6aa5ac6c)</t>
+  </si>
+  <si>
+    <t>Floating pin XFORCE_CAPACITORGOODpuget1.GND(GND)</t>
+  </si>
+  <si>
+    <t>Floating pin XFORCE_CAPACITORGOODpuget1.register_enable_capacitorgood_xd_enable_capacitorgood_32c14a0d(register_enable_capacitorgood_xd_enable_capacitorgood_32c14a0d)</t>
+  </si>
+  <si>
+    <t>Floating Outputs</t>
+  </si>
+  <si>
+    <t>No Connects - Customer</t>
+  </si>
+  <si>
+    <t>No Connects - Celera</t>
+  </si>
+  <si>
     <t>XCAPACITORGOODpuget1,XDEBUG</t>
   </si>
   <si>
-    <t>Floating pin XDEBUG.dft_startup(dft_startup)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.dft_capdetect(dft_capdetect)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.dft_risedelay(dft_risedelay)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.DFT_CAPREFinput(DFT_CAPREFinput)</t>
-  </si>
-  <si>
-    <t>Floating pin V_GNDx.MINUS(0)</t>
-  </si>
-  <si>
-    <t>Floating pin VI__CAPGD.PLUS(59)</t>
-  </si>
-  <si>
-    <t>Xsim_CAPACITORGOODpuget_ROW8</t>
-  </si>
-  <si>
-    <t>Floating pin XCAPACITORGOODpuget1.ok_capacitorgood(ok_capacitorgood)</t>
-  </si>
-  <si>
-    <t>Floating pin XCAPACITORGOODpuget1.status_chrg_status_xdatamap1_6aa5ac6c(status_chrg_status_xdatamap1_6aa5ac6c)</t>
-  </si>
-  <si>
-    <t>Floating pin XFORCE_CAPACITORGOODpuget1.GND(GND)</t>
-  </si>
-  <si>
-    <t>Floating pin XFORCE_CAPACITORGOODpuget1.register_enable_capacitorgood_xd_enable_capacitorgood_32c14a0d(register_enable_capacitorgood_xd_enable_capacitorgood_32c14a0d)</t>
-  </si>
-  <si>
-    <t>Floating Outputs</t>
-  </si>
-  <si>
-    <t>No Connects - Customer</t>
-  </si>
-  <si>
-    <t>No Connects - Celera</t>
+    <t>XDEBUG.dft_startup net: dft_startup io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.dft_capdetect net: dft_capdetect io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.dft_risedelay net: dft_risedelay io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.DFT_CAPREFinput net: DFT_CAPREFinput io: input</t>
   </si>
   <si>
     <t>XIP.IN net: noconn_IN io: output</t>
@@ -1078,6 +1078,9 @@
   </si>
   <si>
     <t>9</t>
+  </si>
+  <si>
+    <t>noconn</t>
   </si>
   <si>
     <t>dbuf</t>
@@ -3521,7 +3524,7 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -3571,7 +3574,7 @@
         <v>342</v>
       </c>
       <c r="B8" t="s">
-        <v>201</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -3579,7 +3582,7 @@
         <v>343</v>
       </c>
       <c r="B9" t="s">
-        <v>134</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -3595,7 +3598,7 @@
         <v>345</v>
       </c>
       <c r="B11" t="s">
-        <v>326</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -3651,6 +3654,14 @@
         <v>352</v>
       </c>
       <c r="B18" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>353</v>
+      </c>
+      <c r="B19" t="s">
         <v>326</v>
       </c>
     </row>
@@ -3666,85 +3677,85 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>357</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B5" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C5" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D5" t="s">
+        <v>362</v>
+      </c>
+      <c r="E5" t="s">
+        <v>363</v>
+      </c>
+      <c r="F5" t="s">
+        <v>364</v>
+      </c>
+      <c r="G5" t="s">
+        <v>365</v>
+      </c>
+      <c r="H5" t="s">
+        <v>366</v>
+      </c>
+      <c r="I5" t="s">
         <v>361</v>
       </c>
-      <c r="E5" t="s">
-        <v>362</v>
-      </c>
-      <c r="F5" t="s">
-        <v>363</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="J5" t="s">
+        <v>367</v>
+      </c>
+      <c r="K5" t="s">
         <v>364</v>
       </c>
-      <c r="H5" t="s">
-        <v>365</v>
-      </c>
-      <c r="I5" t="s">
-        <v>360</v>
-      </c>
-      <c r="J5" t="s">
-        <v>366</v>
-      </c>
-      <c r="K5" t="s">
-        <v>363</v>
-      </c>
       <c r="L5" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M5" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N5" t="s">
         <v>84</v>
       </c>
       <c r="O5" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="P5" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q5" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="R5" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -3759,22 +3770,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
   </sheetData>
@@ -3789,22 +3800,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
   </sheetData>
@@ -3844,7 +3855,7 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3854,34 +3865,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>322</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
   </sheetData>
@@ -3896,7 +3907,7 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3906,34 +3917,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>322</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
   </sheetData>
@@ -3948,22 +3959,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
   </sheetData>
@@ -3978,7 +3989,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
   </sheetData>
@@ -3993,7 +4004,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
   </sheetData>
@@ -4008,7 +4019,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4023,12 +4034,12 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
   </sheetData>
@@ -4043,7 +4054,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
   </sheetData>
@@ -4058,7 +4069,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
   </sheetData>
@@ -4073,7 +4084,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4088,7 +4099,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
   </sheetData>
@@ -4148,7 +4159,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -4168,32 +4179,32 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:1">
@@ -4204,31 +4215,6 @@
     <row r="15" spans="1:1">
       <c r="A15" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -4238,42 +4224,42 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:1">
@@ -4284,31 +4270,6 @@
     <row r="12" spans="1:1">
       <c r="A12" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -4323,7 +4284,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4338,21 +4299,46 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
         <v>34</v>
       </c>
     </row>

--- a/CAPACITORGOODpuget/project/Address.xlsx
+++ b/CAPACITORGOODpuget/project/Address.xlsx
@@ -318,6 +318,9 @@
     <t>dft_ignore_bricks</t>
   </si>
   <si>
+    <t>Y</t>
+  </si>
+  <si>
     <t>dft_measure</t>
   </si>
   <si>
@@ -385,9 +388,6 @@
   </si>
   <si>
     <t>serdes_memory_bist</t>
-  </si>
-  <si>
-    <t>Y</t>
   </si>
   <si>
     <t>serdes_address</t>
@@ -2072,12 +2072,12 @@
         <v>86</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B8" t="s">
         <v>84</v>
@@ -2085,31 +2085,31 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
+        <v>93</v>
+      </c>
+      <c r="B11" t="s">
         <v>92</v>
-      </c>
-      <c r="B11" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -2117,32 +2117,32 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -2155,7 +2155,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B20" t="s">
         <v>84</v>
@@ -2163,15 +2163,15 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B21" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2184,12 +2184,12 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -2202,7 +2202,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B27" t="s">
         <v>84</v>
@@ -2210,7 +2210,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B28" t="s">
         <v>84</v>
@@ -2218,18 +2218,18 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B29" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B30" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -2237,7 +2237,7 @@
         <v>111</v>
       </c>
       <c r="B31" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -2245,7 +2245,7 @@
         <v>112</v>
       </c>
       <c r="B32" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -2306,7 +2306,7 @@
         <v>124</v>
       </c>
       <c r="B40" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2314,7 +2314,7 @@
         <v>125</v>
       </c>
       <c r="B41" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2322,7 +2322,7 @@
         <v>126</v>
       </c>
       <c r="B42" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2359,7 +2359,7 @@
         <v>132</v>
       </c>
       <c r="B47" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2375,7 +2375,7 @@
         <v>135</v>
       </c>
       <c r="B49" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -2383,7 +2383,7 @@
         <v>136</v>
       </c>
       <c r="B50" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2399,7 +2399,7 @@
         <v>139</v>
       </c>
       <c r="B52" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -2608,7 +2608,7 @@
         <v>174</v>
       </c>
       <c r="B83" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -2616,7 +2616,7 @@
         <v>175</v>
       </c>
       <c r="B84" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -2624,7 +2624,7 @@
         <v>176</v>
       </c>
       <c r="B85" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -2632,7 +2632,7 @@
         <v>177</v>
       </c>
       <c r="B86" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -2640,7 +2640,7 @@
         <v>178</v>
       </c>
       <c r="B87" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -2648,7 +2648,7 @@
         <v>179</v>
       </c>
       <c r="B88" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -2656,7 +2656,7 @@
         <v>180</v>
       </c>
       <c r="B89" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -2664,7 +2664,7 @@
         <v>181</v>
       </c>
       <c r="B90" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -2680,7 +2680,7 @@
         <v>184</v>
       </c>
       <c r="B92" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -2704,7 +2704,7 @@
         <v>187</v>
       </c>
       <c r="B95" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -2712,7 +2712,7 @@
         <v>188</v>
       </c>
       <c r="B96" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -2720,7 +2720,7 @@
         <v>189</v>
       </c>
       <c r="B97" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -2728,7 +2728,7 @@
         <v>190</v>
       </c>
       <c r="B98" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -2736,7 +2736,7 @@
         <v>191</v>
       </c>
       <c r="B99" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -2744,7 +2744,7 @@
         <v>192</v>
       </c>
       <c r="B100" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -2752,7 +2752,7 @@
         <v>193</v>
       </c>
       <c r="B101" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -3338,7 +3338,7 @@
         <v>310</v>
       </c>
       <c r="B175" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="176" spans="1:2">
